--- a/results/682_z29/2_canaliculi/682_z29_canaliculi_results.xlsx
+++ b/results/682_z29/2_canaliculi/682_z29_canaliculi_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,441 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>201.3086</v>
+      </c>
+      <c r="D12" t="n">
+        <v>214.1665</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60.6733</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7938.5455</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8595</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2078.1806</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19815</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20090</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4945.8225</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9943</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03152782</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03106522</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0098891</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03455861</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.03359533</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.01017876</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.8431</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.7484</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7371</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>per 100 px</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>177.2727</v>
+      </c>
+      <c r="D20" t="n">
+        <v>174</v>
+      </c>
+      <c r="E20" t="n">
+        <v>70.7758</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>349.3636</v>
+      </c>
+      <c r="D21" t="n">
+        <v>288</v>
+      </c>
+      <c r="E21" t="n">
+        <v>159.2396</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>277.0839</v>
+      </c>
+      <c r="D22" t="n">
+        <v>272.3087</v>
+      </c>
+      <c r="E22" t="n">
+        <v>106.8759</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>775.4374</v>
+      </c>
+      <c r="D23" t="n">
+        <v>767.2569</v>
+      </c>
+      <c r="E23" t="n">
+        <v>337.6027</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6.2727</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.149</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9.454499999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.7514</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>11.4545</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.5247</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>11</v>
       </c>
     </row>
@@ -696,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +1353,63 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>field_length_density_w_per_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.04198674</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>field_density_without_flagged_per_px</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03688309</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>field_density_in_roi_per_px</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
         </is>
       </c>
     </row>
@@ -932,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +1468,81 @@
           <t>mean_edge_length_px</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1002,6 +1569,51 @@
       <c r="H2" t="n">
         <v>34.223</v>
       </c>
+      <c r="I2" t="n">
+        <v>262.0955</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5607</v>
+      </c>
+      <c r="K2" t="n">
+        <v>13819</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03335117</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02974166</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.1446</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>62</v>
+      </c>
+      <c r="R2" t="n">
+        <v>92</v>
+      </c>
+      <c r="S2" t="n">
+        <v>209.9239</v>
+      </c>
+      <c r="T2" t="n">
+        <v>456.5757</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1028,6 +1640,51 @@
       <c r="H3" t="n">
         <v>29.6801</v>
       </c>
+      <c r="I3" t="n">
+        <v>229.5219</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9151</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23871</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04097913</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04608102</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.4855</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>223</v>
+      </c>
+      <c r="R3" t="n">
+        <v>425</v>
+      </c>
+      <c r="S3" t="n">
+        <v>407.3209</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1247.8864</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1711,51 @@
       <c r="H4" t="n">
         <v>23.1892</v>
       </c>
+      <c r="I4" t="n">
+        <v>120.8112</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6134</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17911</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.05037496</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05326336</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.311</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>235</v>
+      </c>
+      <c r="R4" t="n">
+        <v>440</v>
+      </c>
+      <c r="S4" t="n">
+        <v>343.5219</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1052.524</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1782,51 @@
       <c r="H5" t="n">
         <v>31.0853</v>
       </c>
+      <c r="I5" t="n">
+        <v>309.2792</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11331</v>
+      </c>
+      <c r="K5" t="n">
+        <v>28206</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03106522</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04243778</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.5867</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>278</v>
+      </c>
+      <c r="R5" t="n">
+        <v>677</v>
+      </c>
+      <c r="S5" t="n">
+        <v>390.3209</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1326.4478</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" t="n">
+        <v>13</v>
+      </c>
+      <c r="W5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1106,6 +1853,51 @@
       <c r="H6" t="n">
         <v>36.3538</v>
       </c>
+      <c r="I6" t="n">
+        <v>235.2376</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9387</v>
+      </c>
+      <c r="K6" t="n">
+        <v>21888</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02556727</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03207237</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.1255</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>133</v>
+      </c>
+      <c r="R6" t="n">
+        <v>278</v>
+      </c>
+      <c r="S6" t="n">
+        <v>260.3381</v>
+      </c>
+      <c r="T6" t="n">
+        <v>767.2569</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>12</v>
+      </c>
+      <c r="W6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1132,6 +1924,51 @@
       <c r="H7" t="n">
         <v>36.5334</v>
       </c>
+      <c r="I7" t="n">
+        <v>214.1665</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8637</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20090</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.04075489</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.03822797</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.8016</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>283</v>
+      </c>
+      <c r="R7" t="n">
+        <v>523</v>
+      </c>
+      <c r="S7" t="n">
+        <v>399.463</v>
+      </c>
+      <c r="T7" t="n">
+        <v>865.7666</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1158,6 +1995,51 @@
       <c r="H8" t="n">
         <v>23.1667</v>
       </c>
+      <c r="I8" t="n">
+        <v>322.8356</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9940</v>
+      </c>
+      <c r="K8" t="n">
+        <v>22198</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8401999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7724</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03209256</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03225516</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.7878</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>289</v>
+      </c>
+      <c r="R8" t="n">
+        <v>516</v>
+      </c>
+      <c r="S8" t="n">
+        <v>349.0366</v>
+      </c>
+      <c r="T8" t="n">
+        <v>792.3696</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1184,6 +2066,51 @@
       <c r="H9" t="n">
         <v>39.1394</v>
       </c>
+      <c r="I9" t="n">
+        <v>229.4802</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8595</v>
+      </c>
+      <c r="K9" t="n">
+        <v>22042</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02873764</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.03003357</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.1788</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>174</v>
+      </c>
+      <c r="R9" t="n">
+        <v>288</v>
+      </c>
+      <c r="S9" t="n">
+        <v>272.3087</v>
+      </c>
+      <c r="T9" t="n">
+        <v>727.6711</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>10</v>
+      </c>
+      <c r="W9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1210,6 +2137,51 @@
       <c r="H10" t="n">
         <v>37.3304</v>
       </c>
+      <c r="I10" t="n">
+        <v>109.4975</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4245</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11066</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.03368669</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.03533345</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.5663</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>124</v>
+      </c>
+      <c r="R10" t="n">
+        <v>286</v>
+      </c>
+      <c r="S10" t="n">
+        <v>160.6102</v>
+      </c>
+      <c r="T10" t="n">
+        <v>434.8478</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1236,6 +2208,51 @@
       <c r="H11" t="n">
         <v>40.5434</v>
       </c>
+      <c r="I11" t="n">
+        <v>161.8173</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5491</v>
+      </c>
+      <c r="K11" t="n">
+        <v>13376</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02531415</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.02818481</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.4719</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>123</v>
+      </c>
+      <c r="R11" t="n">
+        <v>251</v>
+      </c>
+      <c r="S11" t="n">
+        <v>159.9533</v>
+      </c>
+      <c r="T11" t="n">
+        <v>416.463</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1261,6 +2278,51 @@
       </c>
       <c r="H12" t="n">
         <v>71.2646</v>
+      </c>
+      <c r="I12" t="n">
+        <v>147.196</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6914</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19480</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.01402951</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01806982</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.0381</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>72</v>
+      </c>
+      <c r="R12" t="n">
+        <v>138</v>
+      </c>
+      <c r="S12" t="n">
+        <v>110.8823</v>
+      </c>
+      <c r="T12" t="n">
+        <v>402.9605</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1288,6 +2350,51 @@
       <c r="H13" t="n">
         <v>49.009</v>
       </c>
+      <c r="I13" t="n">
+        <v>254.6934</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9728</v>
+      </c>
+      <c r="K13" t="n">
+        <v>23664</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.03217516</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.03359533</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.7484</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>193</v>
+      </c>
+      <c r="R13" t="n">
+        <v>373</v>
+      </c>
+      <c r="S13" t="n">
+        <v>341.5219</v>
+      </c>
+      <c r="T13" t="n">
+        <v>875.8255</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>14</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1313,6 +2420,51 @@
       </c>
       <c r="H14" t="n">
         <v>26.0794</v>
+      </c>
+      <c r="I14" t="n">
+        <v>202.6934</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7711</v>
+      </c>
+      <c r="K14" t="n">
+        <v>16371</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.9376</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.02412139</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.02284528</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.9601</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>112</v>
+      </c>
+      <c r="R14" t="n">
+        <v>164</v>
+      </c>
+      <c r="S14" t="n">
+        <v>201.6812</v>
+      </c>
+      <c r="T14" t="n">
+        <v>412.1615</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
